--- a/product_upload/packages/60/file.xlsx
+++ b/product_upload/packages/60/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -830,6 +835,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Toxefro</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-DC256DE48997</t>
         </is>
       </c>
@@ -853,7 +863,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1010,6 +1020,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Tagbro</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-613509FE9E13</t>
         </is>
       </c>
@@ -1033,7 +1048,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1194,6 +1209,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Varenya</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-CBAE789A8AF6</t>
         </is>
       </c>
@@ -1217,7 +1237,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1374,6 +1394,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Varenya</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-A930448B5F94</t>
         </is>
       </c>
@@ -1397,7 +1422,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1552,6 +1577,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Zylinamet</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-87C0B4D7AEB9</t>
         </is>
       </c>
@@ -1575,7 +1605,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1732,6 +1762,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>Zylinamet</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-85E1FF2657A8</t>
         </is>
       </c>
@@ -1755,7 +1790,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1916,6 +1951,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>Zylinamet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-EA6DDBB7D491</t>
         </is>
       </c>
@@ -1939,7 +1979,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2100,6 +2140,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>Closa</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-929972BC9336</t>
         </is>
       </c>
@@ -2123,7 +2168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2276,6 +2321,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>Ticaglob</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-05917B895B3E</t>
         </is>
       </c>
@@ -2299,7 +2349,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2460,6 +2510,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>Marvi</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-05D8C2E9D1DE</t>
         </is>
       </c>
@@ -2483,7 +2538,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2644,6 +2699,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>Marvi</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-7D244BCE2688</t>
         </is>
       </c>
@@ -2667,7 +2727,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2824,6 +2884,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>Briglor</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-749095E9D676</t>
         </is>
       </c>
@@ -2847,7 +2912,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3004,6 +3069,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>Briglor</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-A7740394DE45</t>
         </is>
       </c>
@@ -3027,7 +3097,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3188,6 +3258,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>Olmexa Plus</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-0DC59631B1C9</t>
         </is>
       </c>
@@ -3211,7 +3286,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3372,6 +3447,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>Olmexa Plus</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-B74237CD466C</t>
         </is>
       </c>
@@ -3395,7 +3475,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3548,6 +3628,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>Olmexa Plus</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-1EF70B75E8EE</t>
         </is>
       </c>
@@ -3571,7 +3656,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3728,6 +3813,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>Olmexa Plus</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-1A5A895C8A59</t>
         </is>
       </c>
@@ -3751,7 +3841,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3908,6 +3998,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>Olmexa Plus</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-0DC2BFBF1334</t>
         </is>
       </c>
@@ -3931,7 +4026,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4092,6 +4187,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Monovira</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-A2F67F3F6089</t>
         </is>
       </c>
@@ -4115,7 +4215,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4276,6 +4376,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>Olmexa</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-419A7BEB81BB</t>
         </is>
       </c>
@@ -4299,7 +4404,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4456,6 +4561,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Olmexa</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-0329BFB417C9</t>
         </is>
       </c>
@@ -4479,7 +4589,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4640,6 +4750,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>Olmexa</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-09C464874E5D</t>
         </is>
       </c>
@@ -4663,7 +4778,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4820,6 +4935,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>Olmexa</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-C9D71A5F7CAD</t>
         </is>
       </c>
@@ -4843,7 +4963,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5006,6 +5126,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>Solitract Plus</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-8E3425206326</t>
         </is>
       </c>
@@ -5029,7 +5154,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5186,6 +5311,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>Lacosamide QO</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-6A032AEE1934</t>
         </is>
       </c>
@@ -5209,7 +5339,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5366,6 +5496,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>Epixx</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-5DFA6EAD8365</t>
         </is>
       </c>
@@ -5389,7 +5524,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5550,6 +5685,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Epixx</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-B757753F6CB2</t>
         </is>
       </c>
@@ -5573,7 +5713,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5734,6 +5874,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>Epixx</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-4C769032218F</t>
         </is>
       </c>
@@ -5757,7 +5902,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5926,6 +6071,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>Empamac Met</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-3C7FE17B31FF</t>
         </is>
       </c>
@@ -5949,7 +6099,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6106,6 +6256,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>Xitamet</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-7576A7BB73B9</t>
         </is>
       </c>
@@ -6129,7 +6284,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6290,6 +6445,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>Xitamet</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-59AA3E583894</t>
         </is>
       </c>
@@ -6313,7 +6473,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6474,6 +6634,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>Toycin</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-AB56AB3DF4A9</t>
         </is>
       </c>
@@ -6497,7 +6662,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6658,6 +6823,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>Tasylev</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-F584BD907498</t>
         </is>
       </c>
@@ -6681,7 +6851,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6842,6 +7012,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Tasylev</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-24A55D38B685</t>
         </is>
       </c>
@@ -6865,7 +7040,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7022,6 +7197,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Locovab</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-6505C475B689</t>
         </is>
       </c>
@@ -7045,7 +7225,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7206,6 +7386,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>Locovab</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-392ABFD9F371</t>
         </is>
       </c>
@@ -7229,7 +7414,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7386,6 +7571,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>Locovab</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-17F604066189</t>
         </is>
       </c>
@@ -7409,7 +7599,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7570,6 +7760,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>Locovab</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-731DD8D06EA6</t>
         </is>
       </c>
@@ -7593,7 +7788,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7752,6 +7947,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Farinox</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-7EB7D826AAF0</t>
         </is>
       </c>
@@ -7775,7 +7975,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7930,6 +8130,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>ESOXO</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-46EB4F2CB49F</t>
         </is>
       </c>
@@ -7953,7 +8158,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8114,6 +8319,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t xml:space="preserve"> ESOXO</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-3C7D1EF947D2</t>
         </is>
       </c>
@@ -8137,7 +8347,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8294,6 +8504,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>Chinasi</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-4CF465584024</t>
         </is>
       </c>
@@ -8317,7 +8532,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8474,6 +8689,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>Chinasi</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-B6C7411FCFF2</t>
         </is>
       </c>
@@ -8497,7 +8717,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8654,6 +8874,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Chinasi</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-1883E85E7683</t>
         </is>
       </c>
@@ -8677,7 +8902,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8836,6 +9061,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Catafenac</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-E07AAB954C37</t>
         </is>
       </c>
@@ -8859,7 +9089,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9014,6 +9244,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Catafenac</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-43DA45E3BF97</t>
         </is>
       </c>
@@ -9037,7 +9272,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9194,6 +9429,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>FINALLERG</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-A6DB36E34AD1</t>
         </is>
       </c>
@@ -9217,7 +9457,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9376,6 +9616,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>Barolex</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-A0B58A226D65</t>
         </is>
       </c>
@@ -9399,7 +9644,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9556,6 +9801,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>Barolex</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-24AB1974D872</t>
         </is>
       </c>
@@ -9579,7 +9829,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9740,6 +9990,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>Glycimille</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-CC1D6A285AC5</t>
         </is>
       </c>
@@ -9763,7 +10018,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9918,6 +10173,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>ORAP FORTE TAB 4 MG</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-ACFDE492D11D</t>
         </is>
       </c>
@@ -9941,7 +10201,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10106,6 +10366,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>PANADOL EXTRA TAB</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-E741A1DA73D0</t>
         </is>
       </c>
@@ -10129,7 +10394,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10290,6 +10555,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>PANTOZOL 40MG TAB</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-2147ED883F92</t>
         </is>
       </c>
@@ -10313,7 +10583,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10470,6 +10740,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>PANTOZOL 40MG TAB</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-9A4D7F493E1E</t>
         </is>
       </c>
@@ -10493,7 +10768,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10656,6 +10931,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>PANADOL COLD AND FLU DAY F.C. CABLETS</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-87F2FA9538BE</t>
         </is>
       </c>
@@ -10679,7 +10959,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10838,6 +11118,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>OXETINE 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-66AB739625FC</t>
         </is>
       </c>
@@ -10861,7 +11146,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11020,6 +11305,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>OFLACIN 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-91721BD3A539</t>
         </is>
       </c>
@@ -11043,7 +11333,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11202,6 +11492,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>NOVONORM 2MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-DB86D774050C</t>
         </is>
       </c>
@@ -11225,7 +11520,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11384,6 +11679,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>NOVONORM 1MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-38894C4D1374</t>
         </is>
       </c>
@@ -11407,7 +11707,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11570,6 +11870,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>NOVONORM 0.5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-8571A28A9276</t>
         </is>
       </c>
@@ -11593,7 +11898,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11748,6 +12053,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>NOVIRAX CREAM 15 GM</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-27500797D844</t>
         </is>
       </c>
@@ -11771,7 +12081,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11936,6 +12246,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>NOVORAPID FLEXPEN 100U\ML</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-717DDCAA2CAE</t>
         </is>
       </c>
@@ -11959,7 +12274,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12126,6 +12441,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>NOVORAPID PEN FILL 100 I.U - ML</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-69CBC5A650E9</t>
         </is>
       </c>
@@ -12149,7 +12469,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12312,6 +12632,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>NUVARING VAGINAL RING</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-446BE03ACE31</t>
         </is>
       </c>
@@ -12335,7 +12660,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12486,6 +12811,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>NUROFEN 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-C0A06C482AB4</t>
         </is>
       </c>
@@ -12509,7 +12839,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12672,6 +13002,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>OMACE 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-8DB45166AEBA</t>
         </is>
       </c>
@@ -12695,7 +13030,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12858,6 +13193,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>OMACE 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-25EC4EA30E2D</t>
         </is>
       </c>
@@ -12881,7 +13221,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13044,6 +13384,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>OMOL 120MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-84D7F9AD8B3F</t>
         </is>
       </c>
@@ -13067,7 +13412,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13226,6 +13571,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>OMOL 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-A578297AAC9B</t>
         </is>
       </c>
@@ -13249,7 +13599,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13404,6 +13754,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>OPRAZOLE 20MG E.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-BFA4B1082D66</t>
         </is>
       </c>
@@ -13427,7 +13782,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13586,6 +13941,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>OMACE 20MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-595503BE5954</t>
         </is>
       </c>
@@ -13609,7 +13969,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13772,6 +14132,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>OMCET 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-6D557A8C215E</t>
         </is>
       </c>
@@ -13795,7 +14160,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13954,6 +14319,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>OMAFEN 400 MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-FBAF29A5FE5C</t>
         </is>
       </c>
@@ -13977,7 +14347,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14140,6 +14510,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>OMACILLIN 125MG-5ML POWDER FOR ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-3DBD9825C48B</t>
         </is>
       </c>
@@ -14163,7 +14538,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14318,6 +14693,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>OMNICEF 125MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-39F5394A36C5</t>
         </is>
       </c>
@@ -14341,7 +14721,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14496,6 +14876,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>OMNIC OCAS 0.4 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-2142D6772B63</t>
         </is>
       </c>
@@ -14519,7 +14904,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14674,6 +15059,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>PROMETIN 5MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-73E9B97F4E13</t>
         </is>
       </c>
@@ -14697,7 +15087,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14856,6 +15246,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>PROSTA TAB</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-5E0B8CC5E4BA</t>
         </is>
       </c>
@@ -14879,7 +15274,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15038,6 +15433,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>PROPECIA</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-C1F74428292E</t>
         </is>
       </c>
@@ -15061,7 +15461,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15224,6 +15624,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>PRISTIQ 50MG EXTENDED RELEASE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-F63985163454</t>
         </is>
       </c>
@@ -15247,7 +15652,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15402,6 +15807,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>PREGADEX 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-26711D3D7C13</t>
         </is>
       </c>
@@ -15425,7 +15835,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15584,6 +15994,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>QUINOX 750MG F- C TABLET</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-C373C3645864</t>
         </is>
       </c>
@@ -15607,7 +16022,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15770,6 +16185,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>PROTOPIC 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-B8C2635B8118</t>
         </is>
       </c>
@@ -15793,7 +16213,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15952,6 +16372,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>PROTON 40MG E.C TAB</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-E99106428F06</t>
         </is>
       </c>
@@ -15975,7 +16400,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16130,6 +16555,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>PROTON 20MG E.C TABLET</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-4F30750AC6D6</t>
         </is>
       </c>
@@ -16153,7 +16583,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16308,6 +16738,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>PULMICORT METERED AEROSOL 200MCG-DOSE</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-416A1763069C</t>
         </is>
       </c>
@@ -16331,7 +16766,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16482,6 +16917,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>PREGADEX 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-DE8DF12BB040</t>
         </is>
       </c>
@@ -16505,7 +16945,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16656,6 +17096,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>PENTASA 1% ENEMA</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-C2CCFF8762DD</t>
         </is>
       </c>
@@ -16679,7 +17124,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16838,6 +17283,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>NOSPASM 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-FB828BC9523E</t>
         </is>
       </c>
@@ -16861,7 +17311,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17016,6 +17466,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>LUSTRAL 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-E6860668C567</t>
         </is>
       </c>
@@ -17039,7 +17494,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17194,6 +17649,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>MAGNACEF 200MG CAP.</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-8AB64D9E16F7</t>
         </is>
       </c>
@@ -17217,7 +17677,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17372,6 +17832,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>MAGNACEF 100MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-D035A76DCD88</t>
         </is>
       </c>
@@ -17395,7 +17860,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17550,6 +18015,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>MAGNACEF 400MG CAP</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-A821B3110B1C</t>
         </is>
       </c>
@@ -17573,7 +18043,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17728,6 +18198,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>LORINEX 0.5MG-1ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-B076BD7F88DB</t>
         </is>
       </c>
@@ -17751,7 +18226,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17910,6 +18385,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>LORINE 10MG FAST MELTING TABLETS</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-858C61F04BBC</t>
         </is>
       </c>
@@ -17933,7 +18413,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18088,6 +18568,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>LOPRESOR 50MG TABS</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-4313B5F4F802</t>
         </is>
       </c>
@@ -18111,7 +18596,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18270,6 +18755,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>LORVAST 10 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-A4F8A72DBBDD</t>
         </is>
       </c>
@@ -18293,7 +18783,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18448,6 +18938,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>LORVAST 20 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-2A27D70441E5</t>
         </is>
       </c>
@@ -18471,7 +18966,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18626,6 +19121,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>LORVAST 40 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-77895C4B11D1</t>
         </is>
       </c>
@@ -18649,7 +19149,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18799,6 +19299,11 @@
       <c r="AR101" t="inlineStr"/>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>LOTEVAN 5/160MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-FEAAA61A766E</t>
         </is>
@@ -18815,7 +19320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18861,100 +19366,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -18986,7 +19496,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19001,92 +19511,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-27090</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>308.67</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>608</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19118,7 +19633,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19133,92 +19648,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-54984</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>353.99</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>609</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19250,7 +19770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19265,92 +19785,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-38631</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>11.16</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>610</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19382,7 +19907,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19397,92 +19922,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-28559</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>278.75</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>611</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19514,7 +20044,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19529,92 +20059,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-74450</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>446.64</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>612</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19646,7 +20181,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19661,92 +20196,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-21603</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>458.28</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>613</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19778,7 +20318,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19793,92 +20333,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-96326</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>36.61</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>614</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19910,7 +20455,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19925,92 +20470,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-88593</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>15.44</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>615</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20042,7 +20592,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20057,92 +20607,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-62563</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>64.87</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>616</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20174,7 +20729,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20189,92 +20744,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-71750</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>26.17</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>617</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20306,7 +20866,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20321,92 +20881,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-53164</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>274.12</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>618</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20423,7 +20988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20529,6 +21094,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20564,7 +21139,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20629,6 +21204,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-A6D3B870F78A</t>
         </is>
@@ -20665,7 +21250,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20730,6 +21315,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-A29E80E2950C</t>
         </is>
@@ -20766,7 +21361,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -20831,6 +21426,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-FC7FE8CE14D6</t>
         </is>
@@ -20867,7 +21472,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -20932,6 +21537,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-80C43E0CB8A6</t>
         </is>
@@ -20968,7 +21583,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21033,6 +21648,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-014F44BC79A5</t>
         </is>
@@ -21069,7 +21694,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21134,6 +21759,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-8A37617492E2</t>
         </is>
@@ -21170,7 +21805,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21235,6 +21870,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-ED2602C21852</t>
         </is>
@@ -21271,7 +21916,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21336,6 +21981,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-D519983ED862</t>
         </is>
@@ -21372,7 +22027,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21437,6 +22092,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-DD7860905CE9</t>
         </is>
@@ -21473,7 +22138,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21538,6 +22203,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-D5D0775E92E2</t>
         </is>
@@ -21574,7 +22249,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21639,6 +22314,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-AAD898874C42</t>
         </is>
@@ -21675,7 +22360,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21740,6 +22425,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-FA8AEC712A9C</t>
         </is>
@@ -21776,7 +22471,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21841,6 +22536,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-DF3C04CA29EF</t>
         </is>
@@ -21877,7 +22582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -21942,6 +22647,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-664E2E3D6C1C</t>
         </is>
@@ -21978,7 +22693,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22043,6 +22758,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-B197E910F66E</t>
         </is>
@@ -22079,7 +22804,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22144,6 +22869,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-2DD0AF6D5122</t>
         </is>
@@ -22180,7 +22915,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22245,6 +22980,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-0644125D78E0</t>
         </is>
@@ -22281,7 +23026,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22346,6 +23091,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-397CBFCBE371</t>
         </is>
@@ -22382,7 +23137,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22447,6 +23202,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-3054D6479871</t>
         </is>
@@ -22483,7 +23248,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22548,6 +23313,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-78C29FBB0856</t>
         </is>

--- a/product_upload/packages/60/file.xlsx
+++ b/product_upload/packages/60/file.xlsx
@@ -686,8 +686,16 @@
           <t>4866009616-404-729505843454</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Toxefro</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Toxefro detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -871,8 +879,16 @@
           <t>2250480087-319-162280135484</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tagbro</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Tagbro detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1056,8 +1072,16 @@
           <t>4880650982-288-090538519284</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Varenya</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Varenya detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1245,8 +1269,16 @@
           <t>7180608511-798-159744576161</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Varenya</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Varenya detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1430,8 +1462,16 @@
           <t>7430823346-035-907007326630</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zylinamet</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Zylinamet detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1613,8 +1653,16 @@
           <t>5946076919-529-109302100943</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zylinamet</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Zylinamet detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1798,8 +1846,16 @@
           <t>6031241473-087-426621054878</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zylinamet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Zylinamet detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1987,8 +2043,16 @@
           <t>6914519434-282-125114392961</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Closa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Closa detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2176,8 +2240,16 @@
           <t>3803939154-277-363598897754</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ticaglob</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ticaglob detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2357,8 +2429,16 @@
           <t>5714131843-963-713796518792</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Marvi</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Marvi detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2546,8 +2626,16 @@
           <t>2083963545-611-256085012386</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Marvi</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Marvi detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2735,8 +2823,16 @@
           <t>1302260972-650-001740281169</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Briglor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Briglor detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2920,8 +3016,16 @@
           <t>2852050383-086-944247048112</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Briglor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Briglor detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3105,8 +3209,16 @@
           <t>7902640000-475-344112110230</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmexa Plus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Olmexa Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3294,8 +3406,16 @@
           <t>0247231678-639-061958994038</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmexa Plus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Olmexa Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3483,8 +3603,16 @@
           <t>4860051038-405-529716831575</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmexa Plus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Olmexa Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3664,8 +3792,16 @@
           <t>4687563405-586-479745988112</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmexa Plus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Olmexa Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3849,8 +3985,16 @@
           <t>9987192317-466-842831506758</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmexa Plus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Olmexa Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4034,8 +4178,16 @@
           <t>7255549100-938-386544184790</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Monovira</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Monovira detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4223,8 +4375,16 @@
           <t>2387718298-368-762788717995</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmexa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Olmexa detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4412,8 +4572,16 @@
           <t>7780435332-769-634590686683</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmexa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Olmexa detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4597,8 +4765,16 @@
           <t>2946914816-015-838108405428</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmexa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Olmexa detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4786,8 +4962,16 @@
           <t>4615739821-470-486588824966</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmexa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Olmexa detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5162,8 +5346,16 @@
           <t>9260021704-533-666889154203</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lacosamide QO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Lacosamide QO detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5347,8 +5539,16 @@
           <t>1563633657-415-103438642679</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Epixx</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Epixx detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5532,8 +5732,16 @@
           <t>3862829658-833-731190317203</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Epixx</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Epixx detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5721,8 +5929,16 @@
           <t>1927066932-089-840793880678</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Epixx</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Epixx detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6107,8 +6323,16 @@
           <t>9960027411-448-786748903259</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xitamet</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Xitamet detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6292,8 +6516,16 @@
           <t>7546353489-242-927732763780</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xitamet</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Xitamet detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6481,8 +6713,16 @@
           <t>3333779045-234-423982861801</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Toycin</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Toycin detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6670,8 +6910,16 @@
           <t>9062347036-421-210467183973</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tasylev</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Tasylev detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6859,8 +7107,16 @@
           <t>2557764491-762-126624263397</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tasylev</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tasylev detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7048,8 +7304,16 @@
           <t>7630717645-452-565463494345</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Locovab</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Locovab detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7233,8 +7497,16 @@
           <t>8531949038-514-804213803301</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Locovab</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Locovab detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7422,8 +7694,16 @@
           <t>4732941412-549-288258209741</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Locovab</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Locovab detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7607,8 +7887,16 @@
           <t>6407214110-270-021002690969</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Locovab</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Locovab detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7796,8 +8084,16 @@
           <t>1160507944-058-590750340577</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Farinox</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Farinox detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -7983,8 +8279,16 @@
           <t>3045562196-111-437613015819</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESOXO</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ESOXO detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8166,8 +8470,16 @@
           <t>5675510357-776-277326784806</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESOXO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ESOXO detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8355,8 +8667,16 @@
           <t>5668559367-792-830690219003</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Chinasi</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Chinasi detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8540,8 +8860,16 @@
           <t>8967855105-647-309041518835</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Chinasi</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Chinasi detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8725,8 +9053,16 @@
           <t>9620348595-850-581028580060</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Chinasi</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Chinasi detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -8910,8 +9246,16 @@
           <t>9045960227-685-954548210648</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Catafenac</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Catafenac detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9097,8 +9441,16 @@
           <t>0181179134-121-266129640686</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Catafenac</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Catafenac detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9280,8 +9632,16 @@
           <t>5292586946-891-060002094984</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FINALLERG</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>FINALLERG detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9465,8 +9825,16 @@
           <t>4210390487-634-845631860295</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Barolex</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Barolex detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9652,8 +10020,16 @@
           <t>1448154863-105-054294190022</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Barolex</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Barolex detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9837,8 +10213,16 @@
           <t>3761096115-470-457904899761</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Glycimille</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Glycimille detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10026,8 +10410,16 @@
           <t>9082549424-482-481299795220</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORAP FORTE TAB 4 MG</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ORAP FORTE TAB 4 MG detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10209,8 +10601,16 @@
           <t>2184312692-475-639502598524</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANADOL EXTRA TAB</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PANADOL EXTRA TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -10402,8 +10802,16 @@
           <t>5626891779-931-892236192937</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANTOZOL 40MG TAB</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PANTOZOL 40MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>BATTERJEE PHARMACETICAL FACTORY</t>
@@ -10591,8 +10999,16 @@
           <t>4012642515-507-774165580974</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANTOZOL 40MG TAB</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PANTOZOL 40MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>BATTERJEE PHARMACETICAL FACTORY</t>
@@ -10776,8 +11192,16 @@
           <t>0683852444-077-056811169462</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANADOL COLD AND FLU DAY F.C. CABLETS</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PANADOL COLD AND FLU DAY F.C. CABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -10967,8 +11391,16 @@
           <t>8461869394-051-786145284243</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OXETINE 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>OXETINE 20MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11154,8 +11586,16 @@
           <t>5961719423-165-270846198315</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OFLACIN 200MG TAB</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>OFLACIN 200MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11341,8 +11781,16 @@
           <t>3477559358-149-223578370266</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOVONORM 2MG TABLET</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>NOVONORM 2MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11528,8 +11976,16 @@
           <t>4440953176-582-459735950963</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOVONORM 1MG TABLET</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>NOVONORM 1MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11715,8 +12171,16 @@
           <t>1343501326-938-700716311463</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOVONORM 0.5MG TABLET</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>NOVONORM 0.5MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -11906,8 +12370,16 @@
           <t>4286890163-333-684139276523</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOVIRAX CREAM 15 GM</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>NOVIRAX CREAM 15 GM detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12089,8 +12561,16 @@
           <t>3918943272-670-335416071029</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOVORAPID FLEXPEN 100U\ML</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>NOVORAPID FLEXPEN 100U\ML detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>Saudi Biotechnology Manufacturing Co</t>
@@ -12282,8 +12762,16 @@
           <t>4342764554-667-910427716828</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOVORAPID PEN FILL 100 I.U - ML</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>NOVORAPID PEN FILL 100 I.U - ML detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12477,8 +12965,16 @@
           <t>0201997529-174-773609664751</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NUVARING VAGINAL RING</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>NUVARING VAGINAL RING detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12668,8 +13164,16 @@
           <t>4220392228-400-307654008282</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NUROFEN 200MG TAB</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>NUROFEN 200MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12847,8 +13351,16 @@
           <t>0569665998-749-289475540120</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMACE 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>OMACE 10MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13038,8 +13550,16 @@
           <t>6687523804-581-742648609617</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMACE 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>OMACE 5MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13229,8 +13749,16 @@
           <t>5394367161-043-469461799108</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMOL 120MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>OMOL 120MG\5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13420,8 +13948,16 @@
           <t>1338599105-186-696071786446</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMOL 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>OMOL 500MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13607,8 +14143,16 @@
           <t>5305656824-934-399435281690</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OPRAZOLE 20MG E.C.TAB</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>OPRAZOLE 20MG E.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -13790,8 +14334,16 @@
           <t>0624536585-790-388391254354</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMACE 20MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>OMACE 20MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -13977,8 +14529,16 @@
           <t>0711024278-799-935905202463</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMCET 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>OMCET 5MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14168,8 +14728,16 @@
           <t>2236650075-203-559527365304</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMAFEN 400 MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>OMAFEN 400 MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14355,8 +14923,16 @@
           <t>7486491877-233-056612938994</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMACILLIN 125MG-5ML POWDER FOR ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>OMACILLIN 125MG-5ML POWDER FOR ORAL SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14546,8 +15122,16 @@
           <t>8489399783-176-419674908896</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMNICEF 125MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>OMNICEF 125MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14729,8 +15313,16 @@
           <t>4941811787-101-652927440126</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMNIC OCAS 0.4 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>OMNIC OCAS 0.4 MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -14912,8 +15504,16 @@
           <t>4560153793-087-310157902390</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROMETIN 5MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>PROMETIN 5MG\5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15095,8 +15695,16 @@
           <t>8065810003-279-634265878054</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROSTA TAB</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>PROSTA TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15282,8 +15890,16 @@
           <t>5915623343-003-675917259878</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROPECIA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>PROPECIA detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15469,8 +16085,16 @@
           <t>7858968932-210-581961967270</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRISTIQ 50MG EXTENDED RELEASE TABLETS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>PRISTIQ 50MG EXTENDED RELEASE TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15660,8 +16284,16 @@
           <t>9618108918-556-853269933419</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGADEX 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>PREGADEX 75 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -15843,8 +16475,16 @@
           <t>9691316418-389-144542013094</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUINOX 750MG F- C TABLET</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>QUINOX 750MG F- C TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16030,8 +16670,16 @@
           <t>8070149495-254-772937012293</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROTOPIC 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>PROTOPIC 0.1% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16221,8 +16869,16 @@
           <t>1296767797-661-074430908016</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROTON 40MG E.C TAB</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>PROTON 40MG E.C TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16408,8 +17064,16 @@
           <t>4047273592-122-404125515858</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROTON 20MG E.C TABLET</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>PROTON 20MG E.C TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16591,8 +17255,16 @@
           <t>2069833552-711-901357585310</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PULMICORT METERED AEROSOL 200MCG-DOSE</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>PULMICORT METERED AEROSOL 200MCG-DOSE detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16774,8 +17446,16 @@
           <t>9306219147-815-951888609664</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGADEX 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>PREGADEX 150 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -16953,8 +17633,16 @@
           <t>4492500649-668-201362547158</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PENTASA 1% ENEMA</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>PENTASA 1% ENEMA detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17132,8 +17820,16 @@
           <t>7519477054-803-918561489621</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOSPASM 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>NOSPASM 10 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17319,8 +18015,16 @@
           <t>5785040310-929-387941135684</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LUSTRAL 50MG TAB</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>LUSTRAL 50MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17502,8 +18206,16 @@
           <t>1812274802-666-680375444880</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MAGNACEF 200MG CAP.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>MAGNACEF 200MG CAP. detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17685,8 +18397,16 @@
           <t>0321637478-305-356868216788</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MAGNACEF 100MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>MAGNACEF 100MG\5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -17868,8 +18588,16 @@
           <t>3310759838-124-701139629442</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MAGNACEF 400MG CAP</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>MAGNACEF 400MG CAP detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18051,8 +18779,16 @@
           <t>6681045042-551-643101079191</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORINEX 0.5MG-1ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>LORINEX 0.5MG-1ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18234,8 +18970,16 @@
           <t>6594275464-242-859344407790</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORINE 10MG FAST MELTING TABLETS</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>LORINE 10MG FAST MELTING TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18421,8 +19165,16 @@
           <t>9562050121-436-718604429920</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOPRESOR 50MG TABS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>LOPRESOR 50MG TABS detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18604,8 +19356,16 @@
           <t>4638529662-662-504498035749</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORVAST 10 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>LORVAST 10 MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -18791,8 +19551,16 @@
           <t>1127110066-151-371742139212</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORVAST 20 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>LORVAST 20 MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -18974,8 +19742,16 @@
           <t>7301062672-013-259686014289</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORVAST 40 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>LORVAST 40 MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19157,8 +19933,16 @@
           <t>3599091094-726-682981654039</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOTEVAN 5/160MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>LOTEVAN 5/160MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/60/file.xlsx
+++ b/product_upload/packages/60/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20150,7 +20150,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21853,40 +21853,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21966,38 +21971,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>209.08</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-A6D3B870F78A</t>
         </is>
@@ -22077,38 +22087,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>278.24</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-A29E80E2950C</t>
         </is>
@@ -22188,38 +22203,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>391.67</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-FC7FE8CE14D6</t>
         </is>
@@ -22299,38 +22319,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>290.43</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-80C43E0CB8A6</t>
         </is>
@@ -22410,38 +22435,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>53.3</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-014F44BC79A5</t>
         </is>
@@ -22521,38 +22551,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>400.84</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-8A37617492E2</t>
         </is>
@@ -22632,38 +22667,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>151.8</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-ED2602C21852</t>
         </is>
@@ -22743,38 +22783,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>450.91</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-D519983ED862</t>
         </is>
@@ -22854,38 +22899,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>278.46</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-DD7860905CE9</t>
         </is>
@@ -22965,38 +23015,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>129.34</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-D5D0775E92E2</t>
         </is>
@@ -23076,38 +23131,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>428.88</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-AAD898874C42</t>
         </is>
@@ -23187,38 +23247,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>204.18</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-FA8AEC712A9C</t>
         </is>
@@ -23298,38 +23363,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>204.68</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-DF3C04CA29EF</t>
         </is>
@@ -23409,38 +23479,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>40.29</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-664E2E3D6C1C</t>
         </is>
@@ -23520,38 +23595,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>251.07</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-B197E910F66E</t>
         </is>
@@ -23631,38 +23711,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>79.05</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-2DD0AF6D5122</t>
         </is>
@@ -23742,38 +23827,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>417.16</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-0644125D78E0</t>
         </is>
@@ -23853,38 +23943,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>259.89</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-397CBFCBE371</t>
         </is>
@@ -23964,38 +24059,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>76.78</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-3054D6479871</t>
         </is>
@@ -24075,38 +24175,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>347.15</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-78C29FBB0856</t>
         </is>
